--- a/test-exports/rates-2020-01-01-to-2030-01-01.xlsx
+++ b/test-exports/rates-2020-01-01-to-2030-01-01.xlsx
@@ -4,19 +4,25 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Data Export" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Daily rates" state="visible" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Daily rates'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>Kusum ERP - Daily metal rates</t>
-  </si>
-  <si>
-    <t>Rate date: 2020-01-01 to 2030-01-01 | 2 rows</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+  <si>
+    <t>Daily Metal Rate Register</t>
+  </si>
+  <si>
+    <t>01-01-2020 to 01-01-2030 (India Standard Time) | 3 saved rates</t>
+  </si>
+  <si>
+    <t>Rate days</t>
   </si>
   <si>
     <t>Rate date</t>
@@ -41,11 +47,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="₹#,##0.00"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="#,##0;[Red]-#,##0"/>
+    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="166" formatCode="[$₹-en-IN]#,##0.00;[Red]-[$₹-en-IN]#,##0.00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -65,10 +72,20 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF6E4B12"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF30251D"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FF271A05"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -82,7 +99,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFF4DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFBF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD5A044"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFCF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -110,9 +147,15 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="thin">
+        <color rgb="FFE8E1D8"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE8E1D8"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE8E1D8"/>
+      </top>
       <bottom style="thin">
         <color rgb="FFE8E1D8"/>
       </bottom>
@@ -122,23 +165,38 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -158,8 +216,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="KusumExport1" displayName="KusumExport1" ref="A4:E6" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A4:E6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="KusumExport1" displayName="KusumExport1" ref="A5:E8" totalsRowShown="1" headerRowCount="1">
+  <autoFilter ref="A5:E8">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -173,7 +231,7 @@
     <tableColumn id="4" name="Silver / g" totalsRowFunction="none"/>
     <tableColumn id="5" name="Note" totalsRowFunction="none"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -502,11 +560,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="4" width="16" customWidth="1"/>
+    <col min="2" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="34" customWidth="1"/>
   </cols>
   <sheetData>
@@ -528,62 +586,92 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="4" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B3" s="4">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+    </row>
+    <row r="5" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="C5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="D5" s="5" t="s">
         <v>6</v>
       </c>
+      <c r="E5" s="5" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>46255.27083333333</v>
-      </c>
-      <c r="B5" s="5">
+    <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>46255.5</v>
+      </c>
+      <c r="B6" s="7">
         <v>2000</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C6" s="7">
         <v>3000</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D6" s="7">
         <v>1000</v>
       </c>
-      <c r="E5" s="6"/>
+      <c r="E6" s="8"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <v>46261.27083333333</v>
-      </c>
-      <c r="B6" s="5">
+    <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
+        <v>46261.5</v>
+      </c>
+      <c r="B7" s="10">
         <v>7350</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C7" s="10">
         <v>7950</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D7" s="10">
         <v>94</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>7</v>
+      <c r="E7" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>46262.5</v>
+      </c>
+      <c r="B8" s="7">
+        <v>7350</v>
+      </c>
+      <c r="C8" s="7">
+        <v>7950</v>
+      </c>
+      <c r="D8" s="7">
+        <v>94</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E6"/>
+  <autoFilter ref="A5:E8"/>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;LKusum ERP&amp;CConfidential business register&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenFooter>&amp;LKusum ERP&amp;CConfidential business register&amp;RPage &amp;P of &amp;N</evenFooter>
+  </headerFooter>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>

--- a/test-exports/rates-2020-01-01-to-2030-01-01.xlsx
+++ b/test-exports/rates-2020-01-01-to-2030-01-01.xlsx
@@ -213,26 +213,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="KusumExport1" displayName="KusumExport1" ref="A5:E8" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A5:E8">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-    <filterColumn colId="4" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Rate date" totalsRowLabel="Total"/>
-    <tableColumn id="2" name="22K gold / g" totalsRowFunction="none"/>
-    <tableColumn id="3" name="24K gold / g" totalsRowFunction="none"/>
-    <tableColumn id="4" name="Silver / g" totalsRowFunction="none"/>
-    <tableColumn id="5" name="Note" totalsRowFunction="none"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -672,8 +652,5 @@
     <oddFooter>&amp;LKusum ERP&amp;CConfidential business register&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenFooter>&amp;LKusum ERP&amp;CConfidential business register&amp;RPage &amp;P of &amp;N</evenFooter>
   </headerFooter>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>